--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260917.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260917.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>25.99%</t>
+          <t>26.03%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>15,685</t>
+          <t>100,190</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.03%</t>
+          <t>8.18%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>100,190</t>
+          <t>15,685</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.94%</t>
+          <t>7.87%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.47%</t>
+          <t>6.65%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.40%</t>
+          <t>5.35%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.64%</t>
+          <t>4.50%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -924,51 +924,51 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>26,578</t>
+          <t>19,490</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>19,490</t>
+          <t>26,578</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -990,73 +990,73 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>59,298</t>
+          <t>11,681</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>11,681</t>
+          <t>59,298</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>76,885,278</t>
+          <t>7,990</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1078,29 +1078,29 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>7,990</t>
+          <t>62,777,359</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1166,46 +1166,46 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>19,587</t>
+          <t>9,536</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>9,536</t>
+          <t>19,587</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1293,34 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>525,826</t>
+          <t>610,404</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>31,024</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
